--- a/output/graficos_dimensiones/comunal_e_basneta_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2018_valparaiso.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Panquehue</t>
   </si>
   <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa María</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:54</t>
+    <t xml:space="preserve">2026-09-09 23:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -671,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5704</v>
+        <v>5703</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2018</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5703</v>
+        <v>5704</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_e_basneta_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:55</t>
+    <t xml:space="preserve">2026-09-18 10:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
